--- a/data/trans_dic/P38B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,7; 90,09</t>
+          <t>85,85; 90,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,51; 91,2</t>
+          <t>86,54; 91,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,66; 92,15</t>
+          <t>86,39; 92,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,44; 94,42</t>
+          <t>91,26; 94,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,56; 94,88</t>
+          <t>91,57; 94,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,42; 95,6</t>
+          <t>92,4; 95,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,58; 92,09</t>
+          <t>89,62; 92,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,01; 92,69</t>
+          <t>90,12; 92,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90,85; 93,75</t>
+          <t>90,63; 93,69</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,71; 79,36</t>
+          <t>75,77; 79,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,47; 81,19</t>
+          <t>77,44; 80,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,95; 78,77</t>
+          <t>47,11; 78,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,15; 85,65</t>
+          <t>82,19; 85,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,83; 86,97</t>
+          <t>83,72; 86,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,14; 87,49</t>
+          <t>74,3; 87,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 81,93</t>
+          <t>79,27; 82,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,22; 83,5</t>
+          <t>81,17; 83,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,14; 82,25</t>
+          <t>61,19; 82,01</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,39; 90,72</t>
+          <t>84,38; 90,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,03; 84,79</t>
+          <t>77,73; 84,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,36; 86,92</t>
+          <t>78,21; 86,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,67; 90,16</t>
+          <t>83,29; 90,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,33; 87,02</t>
+          <t>80,06; 86,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,32; 91,39</t>
+          <t>85,86; 91,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,11; 89,47</t>
+          <t>85,17; 89,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,12; 84,62</t>
+          <t>80,11; 84,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,23; 88,24</t>
+          <t>83,49; 88,29</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,74; 83,31</t>
+          <t>80,76; 83,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,48; 83,26</t>
+          <t>80,28; 83,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,57; 81,66</t>
+          <t>55,74; 81,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,58; 88,88</t>
+          <t>86,51; 88,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,33; 88,45</t>
+          <t>86,15; 88,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 89,01</t>
+          <t>80,4; 88,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,12; 85,87</t>
+          <t>84,05; 85,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,76; 85,61</t>
+          <t>83,79; 85,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,44; 84,63</t>
+          <t>71,87; 84,73</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>828831; 871292</t>
+          <t>830325; 871588</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>649894; 685088</t>
+          <t>650109; 684334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>444704; 472867</t>
+          <t>443309; 472374</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1214385; 1254007</t>
+          <t>1212064; 1251166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>906988; 939929</t>
+          <t>907158; 939850</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>696686; 720705</t>
+          <t>696536; 721141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2056211; 2113830</t>
+          <t>2057036; 2115103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1567818; 1614476</t>
+          <t>1569672; 1616322</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1151080; 1187890</t>
+          <t>1148358; 1187116</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1478080; 1549233</t>
+          <t>1479271; 1552356</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1589811; 1666244</t>
+          <t>1589317; 1660874</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1121029; 1804097</t>
+          <t>1079078; 1802944</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1436495; 1497791</t>
+          <t>1437152; 1499271</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1661919; 1724220</t>
+          <t>1659675; 1724315</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1657874; 1956231</t>
+          <t>1661448; 1955967</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2932913; 3032011</t>
+          <t>2933514; 3036925</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3277238; 3369154</t>
+          <t>3275052; 3370490</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2903194; 3723012</t>
+          <t>2769742; 3712221</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>402879; 433090</t>
+          <t>402820; 432878</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>424441; 461213</t>
+          <t>422842; 459886</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>506695; 562048</t>
+          <t>505750; 561206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>382870; 412558</t>
+          <t>381132; 412888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>440309; 476953</t>
+          <t>438796; 475830</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>570128; 603592</t>
+          <t>567102; 602744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>795723; 836507</t>
+          <t>796351; 838227</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>875010; 924161</t>
+          <t>874880; 925142</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1087888; 1153324</t>
+          <t>1091297; 1154071</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2742383; 2829771</t>
+          <t>2743258; 2832973</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2694038; 2787244</t>
+          <t>2687453; 2780798</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2020874; 2817289</t>
+          <t>1923022; 2812764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3060234; 3141461</t>
+          <t>3057601; 3139695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3039909; 3114565</t>
+          <t>3033421; 3115447</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2945204; 3249287</t>
+          <t>2934700; 3245133</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5830698; 5951423</t>
+          <t>5825346; 5952035</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5753133; 5880184</t>
+          <t>5755481; 5875803</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5001259; 6009073</t>
+          <t>5102821; 6016464</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,85; 90,12</t>
+          <t>85,89; 90,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,54; 91,1</t>
+          <t>86,32; 90,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,39; 92,05</t>
+          <t>83,87; 90,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,26; 94,2</t>
+          <t>91,49; 94,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,57; 94,87</t>
+          <t>91,58; 94,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,4; 95,66</t>
+          <t>92,36; 95,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,62; 92,15</t>
+          <t>89,59; 92,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,12; 92,79</t>
+          <t>89,75; 92,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90,63; 93,69</t>
+          <t>89,53; 92,69</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,77; 79,52</t>
+          <t>75,71; 79,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,44; 80,93</t>
+          <t>77,42; 81,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,11; 78,72</t>
+          <t>74,22; 79,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,19; 85,74</t>
+          <t>82,39; 85,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,72; 86,98</t>
+          <t>83,89; 86,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,3; 87,48</t>
+          <t>81,04; 84,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,27; 82,06</t>
+          <t>79,34; 82,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,17; 83,54</t>
+          <t>81,12; 83,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,19; 82,01</t>
+          <t>78,49; 81,41</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,38; 90,68</t>
+          <t>84,46; 90,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,73; 84,54</t>
+          <t>77,59; 84,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,21; 86,79</t>
+          <t>80,42; 86,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,29; 90,23</t>
+          <t>83,3; 89,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,06; 86,81</t>
+          <t>80,37; 86,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,86; 91,26</t>
+          <t>86,75; 91,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,17; 89,65</t>
+          <t>85,27; 89,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,11; 84,71</t>
+          <t>80,16; 84,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,49; 88,29</t>
+          <t>84,62; 88,69</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,76; 83,4</t>
+          <t>80,73; 83,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,28; 83,07</t>
+          <t>80,48; 83,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,74; 81,53</t>
+          <t>78,16; 81,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,51; 88,83</t>
+          <t>86,8; 88,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,15; 88,48</t>
+          <t>86,1; 88,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,4; 88,9</t>
+          <t>85,42; 87,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,05; 85,87</t>
+          <t>84,14; 85,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,79; 85,54</t>
+          <t>83,88; 85,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,87; 84,73</t>
+          <t>82,54; 84,47</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>459736</t>
+          <t>502660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>710998</t>
+          <t>770925</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1170734</t>
+          <t>1273585</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>830325; 871588</t>
+          <t>830674; 872912</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>650109; 684334</t>
+          <t>648463; 683407</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>443309; 472374</t>
+          <t>483545; 519743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1212064; 1251166</t>
+          <t>1215095; 1252351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>907158; 939850</t>
+          <t>907170; 937743</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>696536; 721141</t>
+          <t>757013; 782206</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2057036; 2115103</t>
+          <t>2056427; 2113849</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1569672; 1616322</t>
+          <t>1563250; 1614859</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1148358; 1187116</t>
+          <t>1249915; 1294056</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1597291</t>
+          <t>1715389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1861259</t>
+          <t>1800485</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3458550</t>
+          <t>3515874</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1479271; 1552356</t>
+          <t>1478068; 1552131</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1589317; 1660874</t>
+          <t>1588864; 1667371</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1079078; 1802944</t>
+          <t>1655542; 1762851</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1437152; 1499271</t>
+          <t>1440637; 1502318</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1659675; 1724315</t>
+          <t>1663204; 1724198</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1661448; 1955967</t>
+          <t>1757733; 1834600</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2933514; 3036925</t>
+          <t>2936152; 3034562</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3275052; 3370490</t>
+          <t>3273176; 3372949</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2769742; 3712221</t>
+          <t>3453258; 3581525</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538308</t>
+          <t>596956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>588319</t>
+          <t>656507</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1126627</t>
+          <t>1253463</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>402820; 432878</t>
+          <t>403219; 434131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>422842; 459886</t>
+          <t>422063; 460410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>505750; 561206</t>
+          <t>572282; 617737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>381132; 412888</t>
+          <t>381178; 411801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>438796; 475830</t>
+          <t>440500; 474307</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>567102; 602744</t>
+          <t>637506; 672114</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>796351; 838227</t>
+          <t>797236; 838359</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>874880; 925142</t>
+          <t>875387; 926465</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1091297; 1154071</t>
+          <t>1223989; 1282935</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2595336</t>
+          <t>2815005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3160576</t>
+          <t>3227917</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5755912</t>
+          <t>6042923</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2743258; 2832973</t>
+          <t>2742235; 2838220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2687453; 2780798</t>
+          <t>2694034; 2783637</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1923022; 2812764</t>
+          <t>2750344; 2868374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3057601; 3139695</t>
+          <t>3067854; 3145123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3033421; 3115447</t>
+          <t>3031740; 3113963</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2934700; 3245133</t>
+          <t>3180697; 3271102</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5825346; 5952035</t>
+          <t>5831742; 5949338</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5755481; 5875803</t>
+          <t>5761212; 5880546</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5102821; 6016464</t>
+          <t>5977716; 6117278</t>
         </is>
       </c>
     </row>
